--- a/artfynd/S 2298-2025 artfynd.xlsx
+++ b/artfynd/S 2298-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ10"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1391,27 +1391,27 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118710287</v>
+        <v>136774572</v>
       </c>
       <c r="B8" t="n">
-        <v>57344</v>
+        <v>57313</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100075</v>
+        <v>100065</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Myrspov</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Limosa lapponica</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1421,14 +1421,14 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>70</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>sträckande SV</t>
+          <t>sträckande S</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1468,7 +1468,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
@@ -1478,12 +1478,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1509,33 +1509,33 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118710287</t>
+          <t>https://artportalen.se/Sighting/136774572</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118710331</v>
+        <v>118710287</v>
       </c>
       <c r="B9" t="n">
-        <v>57546</v>
+        <v>57344</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102963</v>
+        <v>100075</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrattmås</t>
+          <t>Myrspov</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chroicocephalus ridibundus</t>
+          <t>Limosa lapponica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1545,14 +1545,14 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>rastande</t>
+          <t>sträckande SV</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1633,43 +1633,43 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118710331</t>
+          <t>https://artportalen.se/Sighting/118710287</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118710325</v>
+        <v>118710331</v>
       </c>
       <c r="B10" t="n">
-        <v>57569</v>
+        <v>57546</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102967</v>
+        <v>102963</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Havstrut</t>
+          <t>Skrattmås</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Larus marinus</t>
+          <t>Chroicocephalus ridibundus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1756,6 +1756,130 @@
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118710331</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>118710325</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57569</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>102967</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Havstrut</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Larus marinus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>rastande</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Norrnäsudd, ca 200 meter sydväst om reservatet, Sm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>416515</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6296988</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ljungby</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Annerstad</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Roger Karlsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Roger Karlsson, Kerstin Karlsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/118710325</t>
         </is>
@@ -1772,6 +1896,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 2298-2025 artfynd.xlsx
+++ b/artfynd/S 2298-2025 artfynd.xlsx
@@ -1394,7 +1394,7 @@
         <v>136774572</v>
       </c>
       <c r="B8" t="n">
-        <v>57313</v>
+        <v>57326</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/S 2298-2025 artfynd.xlsx
+++ b/artfynd/S 2298-2025 artfynd.xlsx
@@ -1394,7 +1394,7 @@
         <v>136774572</v>
       </c>
       <c r="B8" t="n">
-        <v>57326</v>
+        <v>57328</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/S 2298-2025 artfynd.xlsx
+++ b/artfynd/S 2298-2025 artfynd.xlsx
@@ -1426,11 +1426,7 @@
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>sträckande S</t>
-        </is>
-      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>

--- a/artfynd/S 2298-2025 artfynd.xlsx
+++ b/artfynd/S 2298-2025 artfynd.xlsx
@@ -1394,7 +1394,7 @@
         <v>136774572</v>
       </c>
       <c r="B8" t="n">
-        <v>57328</v>
+        <v>57338</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/S 2298-2025 artfynd.xlsx
+++ b/artfynd/S 2298-2025 artfynd.xlsx
@@ -1394,7 +1394,7 @@
         <v>136774572</v>
       </c>
       <c r="B8" t="n">
-        <v>57338</v>
+        <v>57339</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
